--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119925689</v>
+        <v>119925700</v>
       </c>
       <c r="B6" t="n">
-        <v>57316</v>
+        <v>57326</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1172,20 +1172,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1195,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534777</v>
+        <v>534841</v>
       </c>
       <c r="R6" t="n">
-        <v>6415807</v>
+        <v>6415793</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En hane sågs även tidigare i området</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119925700</v>
+        <v>119925707</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>105564</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,35 +1266,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1310,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534841</v>
+        <v>534880</v>
       </c>
       <c r="R7" t="n">
-        <v>6415793</v>
+        <v>6415806</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1350,7 +1342,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Flertalet vitala små askar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1351,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1377,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119925763</v>
+        <v>119925689</v>
       </c>
       <c r="B8" t="n">
-        <v>57329</v>
+        <v>57316</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,25 +1382,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102977</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1423,7 +1416,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1433,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534933</v>
+        <v>534777</v>
       </c>
       <c r="R8" t="n">
-        <v>6415738</v>
+        <v>6415807</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1473,7 +1466,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
+          <t>En hane sågs även tidigare i området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119925707</v>
+        <v>119925763</v>
       </c>
       <c r="B9" t="n">
-        <v>105564</v>
+        <v>57329</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,35 +1505,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1548,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534880</v>
+        <v>534933</v>
       </c>
       <c r="R9" t="n">
-        <v>6415806</v>
+        <v>6415738</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1588,7 +1589,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flertalet vitala små askar.</t>
+          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,7 +1598,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119925700</v>
+        <v>119925689</v>
       </c>
       <c r="B6" t="n">
-        <v>57326</v>
+        <v>57316</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1172,12 +1172,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1187,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534841</v>
+        <v>534777</v>
       </c>
       <c r="R6" t="n">
-        <v>6415793</v>
+        <v>6415807</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1235,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>En hane sågs även tidigare i området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119925707</v>
+        <v>119925700</v>
       </c>
       <c r="B7" t="n">
-        <v>105564</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,35 +1274,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534880</v>
+        <v>534841</v>
       </c>
       <c r="R7" t="n">
-        <v>6415806</v>
+        <v>6415793</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,7 +1350,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flertalet vitala små askar.</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1359,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119925689</v>
+        <v>119925707</v>
       </c>
       <c r="B8" t="n">
-        <v>57316</v>
+        <v>105564</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,43 +1389,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1426,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534777</v>
+        <v>534880</v>
       </c>
       <c r="R8" t="n">
-        <v>6415807</v>
+        <v>6415806</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1466,7 +1465,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En hane sågs även tidigare i området</t>
+          <t>Flertalet vitala små askar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,6 +1474,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119925689</v>
+        <v>119925707</v>
       </c>
       <c r="B6" t="n">
-        <v>57316</v>
+        <v>105564</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,43 +1151,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534777</v>
+        <v>534880</v>
       </c>
       <c r="R6" t="n">
-        <v>6415807</v>
+        <v>6415806</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En hane sågs även tidigare i området</t>
+          <t>Flertalet vitala små askar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,6 +1236,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1262,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119925700</v>
+        <v>119925763</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>57329</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,33 +1267,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1310,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534841</v>
+        <v>534933</v>
       </c>
       <c r="R7" t="n">
-        <v>6415793</v>
+        <v>6415738</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1350,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119925707</v>
+        <v>119925700</v>
       </c>
       <c r="B8" t="n">
-        <v>105564</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,35 +1390,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1425,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534880</v>
+        <v>534841</v>
       </c>
       <c r="R8" t="n">
-        <v>6415806</v>
+        <v>6415793</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,7 +1466,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flertalet vitala små askar.</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,7 +1475,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1493,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119925763</v>
+        <v>119925689</v>
       </c>
       <c r="B9" t="n">
-        <v>57329</v>
+        <v>57316</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,25 +1505,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534933</v>
+        <v>534777</v>
       </c>
       <c r="R9" t="n">
-        <v>6415738</v>
+        <v>6415807</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
+          <t>En hane sågs även tidigare i området</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>119925707</v>
       </c>
       <c r="B6" t="n">
-        <v>105564</v>
+        <v>105588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119925763</v>
+        <v>119925700</v>
       </c>
       <c r="B7" t="n">
-        <v>57329</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,41 +1267,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1311,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534933</v>
+        <v>534841</v>
       </c>
       <c r="R7" t="n">
-        <v>6415738</v>
+        <v>6415793</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,7 +1343,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119925700</v>
+        <v>119925763</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>57339</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,33 +1382,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534841</v>
+        <v>534933</v>
       </c>
       <c r="R8" t="n">
-        <v>6415793</v>
+        <v>6415738</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,7 +1496,7 @@
         <v>119925689</v>
       </c>
       <c r="B9" t="n">
-        <v>57316</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119925700</v>
+        <v>119925763</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>57339</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,33 +1267,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1303,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534841</v>
+        <v>534933</v>
       </c>
       <c r="R7" t="n">
-        <v>6415793</v>
+        <v>6415738</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119925763</v>
+        <v>119925700</v>
       </c>
       <c r="B8" t="n">
-        <v>57339</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,41 +1390,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534933</v>
+        <v>534841</v>
       </c>
       <c r="R8" t="n">
-        <v>6415738</v>
+        <v>6415793</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119925707</v>
+        <v>119925763</v>
       </c>
       <c r="B6" t="n">
-        <v>105588</v>
+        <v>57339</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,35 +1151,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534880</v>
+        <v>534933</v>
       </c>
       <c r="R6" t="n">
-        <v>6415806</v>
+        <v>6415738</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1235,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet vitala små askar.</t>
+          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1244,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1255,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119925763</v>
+        <v>119925707</v>
       </c>
       <c r="B7" t="n">
-        <v>57339</v>
+        <v>105588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,43 +1274,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1311,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534933</v>
+        <v>534880</v>
       </c>
       <c r="R7" t="n">
-        <v>6415738</v>
+        <v>6415806</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,7 +1350,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
+          <t>Flertalet vitala små askar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,6 +1359,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1378,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119925700</v>
+        <v>119925689</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,16 +1394,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1411,12 +1411,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1426,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534841</v>
+        <v>534777</v>
       </c>
       <c r="R8" t="n">
-        <v>6415793</v>
+        <v>6415807</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1466,7 +1474,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>En hane sågs även tidigare i området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119925689</v>
+        <v>119925700</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,16 +1517,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1526,20 +1534,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534777</v>
+        <v>534841</v>
       </c>
       <c r="R9" t="n">
-        <v>6415807</v>
+        <v>6415793</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>En hane sågs även tidigare i området</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119925763</v>
+        <v>119925707</v>
       </c>
       <c r="B6" t="n">
-        <v>57339</v>
+        <v>105588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,43 +1151,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534933</v>
+        <v>534880</v>
       </c>
       <c r="R6" t="n">
-        <v>6415738</v>
+        <v>6415806</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
+          <t>Flertalet vitala små askar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,6 +1236,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1262,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119925707</v>
+        <v>119925763</v>
       </c>
       <c r="B7" t="n">
-        <v>105588</v>
+        <v>57339</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,35 +1267,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1310,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534880</v>
+        <v>534933</v>
       </c>
       <c r="R7" t="n">
-        <v>6415806</v>
+        <v>6415738</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1350,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flertalet vitala små askar.</t>
+          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,7 +1360,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1378,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119925689</v>
+        <v>119925700</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,16 +1394,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1411,20 +1411,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1434,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534777</v>
+        <v>534841</v>
       </c>
       <c r="R8" t="n">
-        <v>6415807</v>
+        <v>6415793</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,7 +1466,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En hane sågs även tidigare i området</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119925700</v>
+        <v>119925689</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,16 +1509,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1534,12 +1526,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534841</v>
+        <v>534777</v>
       </c>
       <c r="R9" t="n">
-        <v>6415793</v>
+        <v>6415807</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>En hane sågs även tidigare i området</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119925707</v>
+        <v>119925763</v>
       </c>
       <c r="B6" t="n">
-        <v>105588</v>
+        <v>57339</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,35 +1151,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534880</v>
+        <v>534933</v>
       </c>
       <c r="R6" t="n">
-        <v>6415806</v>
+        <v>6415738</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1235,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet vitala små askar.</t>
+          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1244,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1255,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119925763</v>
+        <v>119925689</v>
       </c>
       <c r="B7" t="n">
-        <v>57339</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,25 +1274,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1301,7 +1308,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1311,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534933</v>
+        <v>534777</v>
       </c>
       <c r="R7" t="n">
-        <v>6415738</v>
+        <v>6415807</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,7 +1358,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
+          <t>En hane sågs även tidigare i området</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119925700</v>
+        <v>119925707</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>105588</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,35 +1397,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1426,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534841</v>
+        <v>534880</v>
       </c>
       <c r="R8" t="n">
-        <v>6415793</v>
+        <v>6415806</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1466,7 +1473,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Flertalet vitala små askar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,6 +1482,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1493,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119925689</v>
+        <v>119925700</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,16 +1517,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1526,20 +1534,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534777</v>
+        <v>534841</v>
       </c>
       <c r="R9" t="n">
-        <v>6415807</v>
+        <v>6415793</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>En hane sågs även tidigare i området</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119925763</v>
+        <v>119925707</v>
       </c>
       <c r="B6" t="n">
-        <v>57339</v>
+        <v>105588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,43 +1151,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534933</v>
+        <v>534880</v>
       </c>
       <c r="R6" t="n">
-        <v>6415738</v>
+        <v>6415806</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
+          <t>Flertalet vitala små askar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,6 +1236,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1385,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119925707</v>
+        <v>119925763</v>
       </c>
       <c r="B8" t="n">
-        <v>105588</v>
+        <v>57339</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,35 +1390,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1433,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534880</v>
+        <v>534933</v>
       </c>
       <c r="R8" t="n">
-        <v>6415806</v>
+        <v>6415738</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1473,7 +1474,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flertalet vitala små askar.</t>
+          <t>Fågeln hördes även några dagar tidigare i området. Mycket lämplig revir med tanke på mängden äldre lövträd i området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,7 +1483,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119925707</v>
+        <v>119925700</v>
       </c>
       <c r="B6" t="n">
-        <v>105588</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,35 +1151,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534880</v>
+        <v>534841</v>
       </c>
       <c r="R6" t="n">
-        <v>6415806</v>
+        <v>6415793</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet vitala små askar.</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1236,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1501,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119925700</v>
+        <v>119925707</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>105588</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,35 +1512,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1549,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534841</v>
+        <v>534880</v>
       </c>
       <c r="R9" t="n">
-        <v>6415793</v>
+        <v>6415806</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1589,7 +1588,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Flertalet vitala små askar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,6 +1597,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1257,11 +1257,11 @@
         <v>119925689</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>57484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1257,7 +1257,7 @@
         <v>119925689</v>
       </c>
       <c r="B7" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1614,6 +1614,133 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125317937</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Krutebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>534830</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6415808</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tidersrum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Förutom att hanen observerades ett flertal gånger så har även mycket hackspår,  färska som äldre, noterats i den återstående anslutande gamla kontinuitetsskogen på andra sidan skogsvägen samt i den äldre löv och blandskogen på västsidan om skogsvägen och söder om kraftledningar.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,708 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125342831</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Krutebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>534860</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6415818</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tidersrum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125342313</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105676</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Krutebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>534857</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6415831</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tidersrum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>En gammal och hundratals smaskar som kommer köras sönder vid planerad gallring av miljöcertifierade Holmen Skog, som har snitslad för avverkning åt markägaren utan hänsyn till de rödlistade och hotade askarna. Den lövrika blandskogen är dessutom en viktig fågellokal.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125343064</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102326</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Krutebo , Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>534848</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6415833</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tidersrum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125342702</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Krutebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>534824</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6415821</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tidersrum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125342792</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Krutebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>534837</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6415804</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tidersrum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mycket upprörd och långvarig varningsläte och länge på platsen utan att ge sig av indikerar troligen häckning i närheten.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125342993</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57532</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Krutebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>534801</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6415816</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tidersrum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1743,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125342831</v>
+        <v>125342792</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,31 +1755,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1787,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534860</v>
+        <v>534837</v>
       </c>
       <c r="R11" t="n">
-        <v>6415818</v>
+        <v>6415804</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1825,13 +1833,17 @@
           <t>2025-05-22</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket upprörd och långvarig varningsläte och länge på platsen utan att ge sig av indikerar troligen häckning i närheten.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1850,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125342313</v>
+        <v>125342831</v>
       </c>
       <c r="B12" t="n">
-        <v>105676</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,32 +1874,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1898,10 +1906,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534857</v>
+        <v>534860</v>
       </c>
       <c r="R12" t="n">
-        <v>6415831</v>
+        <v>6415818</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1934,11 +1942,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>En gammal och hundratals smaskar som kommer köras sönder vid planerad gallring av miljöcertifierade Holmen Skog, som har snitslad för avverkning åt markägaren utan hänsyn till de rödlistade och hotade askarna. Den lövrika blandskogen är dessutom en viktig fågellokal.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125343064</v>
+        <v>125342993</v>
       </c>
       <c r="B13" t="n">
-        <v>102326</v>
+        <v>57532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,25 +1981,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223246</v>
+        <v>102977</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2004,20 +2007,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Krutebo , Ög</t>
+          <t>Krutebo, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534848</v>
+        <v>534801</v>
       </c>
       <c r="R13" t="n">
-        <v>6415833</v>
+        <v>6415816</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2052,18 +2067,12 @@
           <t>2025-05-22</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2082,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125342702</v>
+        <v>125342313</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>105676</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,47 +2103,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2142,10 +2139,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534824</v>
+        <v>534857</v>
       </c>
       <c r="R14" t="n">
-        <v>6415821</v>
+        <v>6415831</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2180,12 +2177,18 @@
           <t>2025-05-22</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>En gammal och hundratals smaskar som kommer köras sönder vid planerad gallring av miljöcertifierade Holmen Skog, som har snitslad för avverkning åt markägaren utan hänsyn till de rödlistade och hotade askarna. Den lövrika blandskogen är dessutom en viktig fågellokal.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2204,10 +2207,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125342792</v>
+        <v>125342702</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,21 +2223,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2242,11 +2245,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2256,10 +2267,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534837</v>
+        <v>534824</v>
       </c>
       <c r="R15" t="n">
-        <v>6415804</v>
+        <v>6415821</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2292,11 +2303,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Mycket upprörd och långvarig varningsläte och länge på platsen utan att ge sig av indikerar troligen häckning i närheten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,10 +2329,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125342993</v>
+        <v>125343064</v>
       </c>
       <c r="B16" t="n">
-        <v>57532</v>
+        <v>102326</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,25 +2341,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>223246</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2361,32 +2367,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Krutebo, Ög</t>
+          <t>Krutebo , Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534801</v>
+        <v>534848</v>
       </c>
       <c r="R16" t="n">
-        <v>6415816</v>
+        <v>6415833</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2421,12 +2415,18 @@
           <t>2025-05-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1743,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125342792</v>
+        <v>125342831</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,39 +1755,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1795,10 +1787,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534837</v>
+        <v>534860</v>
       </c>
       <c r="R11" t="n">
-        <v>6415804</v>
+        <v>6415818</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1833,17 +1825,13 @@
           <t>2025-05-22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mycket upprörd och långvarig varningsläte och länge på platsen utan att ge sig av indikerar troligen häckning i närheten.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1862,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125342831</v>
+        <v>125342792</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1874,31 +1862,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1906,10 +1902,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534860</v>
+        <v>534837</v>
       </c>
       <c r="R12" t="n">
-        <v>6415818</v>
+        <v>6415804</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1944,13 +1940,17 @@
           <t>2025-05-22</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mycket upprörd och långvarig varningsläte och länge på platsen utan att ge sig av indikerar troligen häckning i närheten.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125342993</v>
+        <v>125342702</v>
       </c>
       <c r="B13" t="n">
-        <v>57532</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,25 +1981,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534801</v>
+        <v>534824</v>
       </c>
       <c r="R13" t="n">
-        <v>6415816</v>
+        <v>6415821</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125342313</v>
+        <v>125342993</v>
       </c>
       <c r="B14" t="n">
-        <v>105676</v>
+        <v>57532</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,35 +2103,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>102977</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2139,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534857</v>
+        <v>534801</v>
       </c>
       <c r="R14" t="n">
-        <v>6415831</v>
+        <v>6415816</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2177,18 +2189,12 @@
           <t>2025-05-22</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>En gammal och hundratals smaskar som kommer köras sönder vid planerad gallring av miljöcertifierade Holmen Skog, som har snitslad för avverkning åt markägaren utan hänsyn till de rödlistade och hotade askarna. Den lövrika blandskogen är dessutom en viktig fågellokal.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2207,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125342702</v>
+        <v>125343064</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>102326</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2219,25 +2225,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>223246</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2245,32 +2251,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krutebo, Ög</t>
+          <t>Krutebo , Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534824</v>
+        <v>534848</v>
       </c>
       <c r="R15" t="n">
-        <v>6415821</v>
+        <v>6415833</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2305,12 +2299,18 @@
           <t>2025-05-22</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125343064</v>
+        <v>125342313</v>
       </c>
       <c r="B16" t="n">
-        <v>102326</v>
+        <v>105676</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,30 +2341,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2373,14 +2373,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Krutebo , Ög</t>
+          <t>Krutebo, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534848</v>
+        <v>534857</v>
       </c>
       <c r="R16" t="n">
-        <v>6415833</v>
+        <v>6415831</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
+          <t>En gammal och hundratals smaskar som kommer köras sönder vid planerad gallring av miljöcertifierade Holmen Skog, som har snitslad för avverkning åt markägaren utan hänsyn till de rödlistade och hotade askarna. Den lövrika blandskogen är dessutom en viktig fågellokal.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>125317937</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125342831</v>
+        <v>125342313</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>105853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,28 +1755,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1787,10 +1791,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534860</v>
+        <v>534857</v>
       </c>
       <c r="R11" t="n">
-        <v>6415818</v>
+        <v>6415831</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1823,6 +1827,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En gammal och hundratals smaskar som kommer köras sönder vid planerad gallring av miljöcertifierade Holmen Skog, som har snitslad för avverkning åt markägaren utan hänsyn till de rödlistade och hotade askarna. Den lövrika blandskogen är dessutom en viktig fågellokal.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125342792</v>
+        <v>125342993</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,25 +1871,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1888,8 +1897,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1902,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534837</v>
+        <v>534801</v>
       </c>
       <c r="R12" t="n">
-        <v>6415804</v>
+        <v>6415816</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1938,11 +1955,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mycket upprörd och långvarig varningsläte och länge på platsen utan att ge sig av indikerar troligen häckning i närheten.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,10 +1981,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125342702</v>
+        <v>125342792</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>57793</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,21 +1997,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2007,19 +2019,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2029,10 +2033,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534824</v>
+        <v>534837</v>
       </c>
       <c r="R13" t="n">
-        <v>6415821</v>
+        <v>6415804</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2065,6 +2069,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket upprörd och långvarig varningsläte och länge på platsen utan att ge sig av indikerar troligen häckning i närheten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,10 +2100,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125342993</v>
+        <v>125343064</v>
       </c>
       <c r="B14" t="n">
-        <v>57532</v>
+        <v>102498</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,25 +2112,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>223246</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2129,32 +2138,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Krutebo, Ög</t>
+          <t>Krutebo , Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534801</v>
+        <v>534848</v>
       </c>
       <c r="R14" t="n">
-        <v>6415816</v>
+        <v>6415833</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2189,12 +2186,18 @@
           <t>2025-05-22</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2213,10 +2216,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125343064</v>
+        <v>125342831</v>
       </c>
       <c r="B15" t="n">
-        <v>102326</v>
+        <v>100451</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,46 +2228,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krutebo , Ög</t>
+          <t>Krutebo, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534848</v>
+        <v>534860</v>
       </c>
       <c r="R15" t="n">
-        <v>6415833</v>
+        <v>6415818</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2297,11 +2296,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2329,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125342313</v>
+        <v>125342702</v>
       </c>
       <c r="B16" t="n">
-        <v>105676</v>
+        <v>57632</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,35 +2335,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2377,10 +2383,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534857</v>
+        <v>534824</v>
       </c>
       <c r="R16" t="n">
-        <v>6415831</v>
+        <v>6415821</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2415,18 +2421,12 @@
           <t>2025-05-22</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En gammal och hundratals smaskar som kommer köras sönder vid planerad gallring av miljöcertifierade Holmen Skog, som har snitslad för avverkning åt markägaren utan hänsyn till de rödlistade och hotade askarna. Den lövrika blandskogen är dessutom en viktig fågellokal.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1743,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125342313</v>
+        <v>125342831</v>
       </c>
       <c r="B11" t="n">
-        <v>105853</v>
+        <v>100451</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,32 +1755,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1791,10 +1787,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534857</v>
+        <v>534860</v>
       </c>
       <c r="R11" t="n">
-        <v>6415831</v>
+        <v>6415818</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1827,11 +1823,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En gammal och hundratals smaskar som kommer köras sönder vid planerad gallring av miljöcertifierade Holmen Skog, som har snitslad för avverkning åt markägaren utan hänsyn till de rödlistade och hotade askarna. Den lövrika blandskogen är dessutom en viktig fågellokal.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2100,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125343064</v>
+        <v>125342313</v>
       </c>
       <c r="B14" t="n">
-        <v>102498</v>
+        <v>105853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2112,30 +2103,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2144,14 +2135,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Krutebo , Ög</t>
+          <t>Krutebo, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534848</v>
+        <v>534857</v>
       </c>
       <c r="R14" t="n">
-        <v>6415833</v>
+        <v>6415831</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2188,7 +2179,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
+          <t>En gammal och hundratals smaskar som kommer köras sönder vid planerad gallring av miljöcertifierade Holmen Skog, som har snitslad för avverkning åt markägaren utan hänsyn till de rödlistade och hotade askarna. Den lövrika blandskogen är dessutom en viktig fågellokal.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,10 +2207,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125342831</v>
+        <v>125343064</v>
       </c>
       <c r="B15" t="n">
-        <v>100451</v>
+        <v>102498</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,42 +2219,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>223246</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krutebo, Ög</t>
+          <t>Krutebo , Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534860</v>
+        <v>534848</v>
       </c>
       <c r="R15" t="n">
-        <v>6415818</v>
+        <v>6415833</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2296,6 +2291,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1619,12 +1619,7 @@
         <v>125317937</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,43 +1738,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125342831</v>
+        <v>125342702</v>
       </c>
       <c r="B11" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1787,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534860</v>
+        <v>534824</v>
       </c>
       <c r="R11" t="n">
-        <v>6415818</v>
+        <v>6415821</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1831,7 +1837,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1850,37 +1855,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125342993</v>
+        <v>125343064</v>
       </c>
       <c r="B12" t="n">
-        <v>57629</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102977</v>
+        <v>223246</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1888,32 +1888,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krutebo, Ög</t>
+          <t>Krutebo , Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534801</v>
+        <v>534848</v>
       </c>
       <c r="R12" t="n">
-        <v>6415816</v>
+        <v>6415833</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1948,12 +1936,18 @@
           <t>2025-05-22</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1972,37 +1966,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125342792</v>
+        <v>125342993</v>
       </c>
       <c r="B13" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57645</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2010,8 +1999,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2024,10 +2021,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534837</v>
+        <v>534801</v>
       </c>
       <c r="R13" t="n">
-        <v>6415804</v>
+        <v>6415816</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2060,11 +2057,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mycket upprörd och långvarig varningsläte och länge på platsen utan att ge sig av indikerar troligen häckning i närheten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,12 +2086,7 @@
         <v>125342313</v>
       </c>
       <c r="B14" t="n">
-        <v>105853</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,37 +2194,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125343064</v>
+        <v>125342792</v>
       </c>
       <c r="B15" t="n">
-        <v>102498</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223246</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2245,20 +2227,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krutebo , Ög</t>
+          <t>Krutebo, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534848</v>
+        <v>534837</v>
       </c>
       <c r="R15" t="n">
-        <v>6415833</v>
+        <v>6415804</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2295,7 +2281,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hotad inte enbart av almsjukan utan även av Holmen Skog genom planerad gallring som ej har uppmärksammat almen! Det verkar vara hopplöst med det miljöcertifierade skogsbruket som ej tar hänsyn.</t>
+          <t>Mycket upprörd och långvarig varningsläte och länge på platsen utan att ge sig av indikerar troligen häckning i närheten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2304,7 +2290,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2323,59 +2308,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125342702</v>
+        <v>125342831</v>
       </c>
       <c r="B16" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2383,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534824</v>
+        <v>534860</v>
       </c>
       <c r="R16" t="n">
-        <v>6415821</v>
+        <v>6415818</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2427,6 +2391,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>125343064</v>
       </c>
       <c r="B12" t="n">
-        <v>102553</v>
+        <v>102560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>125342313</v>
       </c>
       <c r="B14" t="n">
-        <v>105908</v>
+        <v>105915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>125342831</v>
       </c>
       <c r="B16" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>125343064</v>
       </c>
       <c r="B12" t="n">
-        <v>102560</v>
+        <v>102563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>125342313</v>
       </c>
       <c r="B14" t="n">
-        <v>105915</v>
+        <v>105918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>125342831</v>
       </c>
       <c r="B16" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 13162-2024 artfynd.xlsx
+++ b/artfynd/A 13162-2024 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>125343064</v>
       </c>
       <c r="B12" t="n">
-        <v>102563</v>
+        <v>102567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>125342313</v>
       </c>
       <c r="B14" t="n">
-        <v>105918</v>
+        <v>105922</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>125342831</v>
       </c>
       <c r="B16" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
